--- a/artfynd/Staverberget SCA artfynd.xlsx
+++ b/artfynd/Staverberget SCA artfynd.xlsx
@@ -1331,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126905224</v>
+        <v>126905284</v>
       </c>
       <c r="B8" t="n">
-        <v>57141</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1342,28 +1342,28 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1373,10 +1373,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495561</v>
+        <v>495898</v>
       </c>
       <c r="R8" t="n">
-        <v>6906667</v>
+        <v>6906855</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1440,39 +1440,39 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126905225</v>
+        <v>126905156</v>
       </c>
       <c r="B9" t="n">
-        <v>57141</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495563</v>
+        <v>495905</v>
       </c>
       <c r="R9" t="n">
-        <v>6906678</v>
+        <v>6906838</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1549,39 +1549,39 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126905237</v>
+        <v>126905157</v>
       </c>
       <c r="B10" t="n">
-        <v>57141</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495929</v>
+        <v>495931</v>
       </c>
       <c r="R10" t="n">
-        <v>6906727</v>
+        <v>6906818</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1658,39 +1658,39 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126905238</v>
+        <v>126905158</v>
       </c>
       <c r="B11" t="n">
-        <v>57141</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495926</v>
+        <v>495946</v>
       </c>
       <c r="R11" t="n">
-        <v>6906708</v>
+        <v>6906789</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1767,27 +1767,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126905284</v>
+        <v>126905159</v>
       </c>
       <c r="B12" t="n">
-        <v>57950</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495898</v>
+        <v>495943</v>
       </c>
       <c r="R12" t="n">
-        <v>6906855</v>
+        <v>6906777</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1876,39 +1876,39 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126905143</v>
+        <v>126905224</v>
       </c>
       <c r="B13" t="n">
-        <v>57953</v>
+        <v>57141</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495498</v>
+        <v>495561</v>
       </c>
       <c r="R13" t="n">
-        <v>6907024</v>
+        <v>6906667</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1985,39 +1985,39 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126905151</v>
+        <v>126905225</v>
       </c>
       <c r="B14" t="n">
-        <v>57953</v>
+        <v>57141</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>495607</v>
+        <v>495563</v>
       </c>
       <c r="R14" t="n">
-        <v>6907149</v>
+        <v>6906678</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2094,39 +2094,39 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126905153</v>
+        <v>126905237</v>
       </c>
       <c r="B15" t="n">
-        <v>57953</v>
+        <v>57141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2136,10 +2136,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>495784</v>
+        <v>495929</v>
       </c>
       <c r="R15" t="n">
-        <v>6907059</v>
+        <v>6906727</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2203,39 +2203,39 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126905155</v>
+        <v>126905238</v>
       </c>
       <c r="B16" t="n">
-        <v>57953</v>
+        <v>57141</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>495797</v>
+        <v>495926</v>
       </c>
       <c r="R16" t="n">
-        <v>6906993</v>
+        <v>6906708</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2312,27 +2312,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126905156</v>
+        <v>126905320</v>
       </c>
       <c r="B17" t="n">
-        <v>57953</v>
+        <v>57144</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>102613</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2344,7 +2344,7 @@
       <c r="K17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2354,10 +2354,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>495905</v>
+        <v>495422</v>
       </c>
       <c r="R17" t="n">
-        <v>6906838</v>
+        <v>6906863</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2421,7 +2421,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126905157</v>
+        <v>126905143</v>
       </c>
       <c r="B18" t="n">
         <v>57953</v>
@@ -2463,10 +2463,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495931</v>
+        <v>495498</v>
       </c>
       <c r="R18" t="n">
-        <v>6906818</v>
+        <v>6907024</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2530,7 +2530,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126905158</v>
+        <v>126905144</v>
       </c>
       <c r="B19" t="n">
         <v>57953</v>
@@ -2572,10 +2572,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495946</v>
+        <v>495384</v>
       </c>
       <c r="R19" t="n">
-        <v>6906789</v>
+        <v>6907363</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2639,7 +2639,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126905159</v>
+        <v>126905145</v>
       </c>
       <c r="B20" t="n">
         <v>57953</v>
@@ -2681,10 +2681,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>495943</v>
+        <v>495474</v>
       </c>
       <c r="R20" t="n">
-        <v>6906777</v>
+        <v>6907344</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2748,39 +2748,39 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126905228</v>
+        <v>126905147</v>
       </c>
       <c r="B21" t="n">
-        <v>57141</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2790,10 +2790,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>495481</v>
+        <v>495488</v>
       </c>
       <c r="R21" t="n">
-        <v>6907010</v>
+        <v>6907230</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2857,39 +2857,39 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126905230</v>
+        <v>126905150</v>
       </c>
       <c r="B22" t="n">
-        <v>57141</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>495428</v>
+        <v>495490</v>
       </c>
       <c r="R22" t="n">
-        <v>6907139</v>
+        <v>6907214</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2966,39 +2966,39 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126905234</v>
+        <v>126905151</v>
       </c>
       <c r="B23" t="n">
-        <v>57141</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3008,10 +3008,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495761</v>
+        <v>495607</v>
       </c>
       <c r="R23" t="n">
-        <v>6906899</v>
+        <v>6907149</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3075,27 +3075,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126905309</v>
+        <v>126905153</v>
       </c>
       <c r="B24" t="n">
-        <v>57144</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102613</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3107,7 +3107,7 @@
       <c r="K24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3117,10 +3117,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495781</v>
+        <v>495784</v>
       </c>
       <c r="R24" t="n">
-        <v>6906930</v>
+        <v>6907059</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3184,27 +3184,27 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126905320</v>
+        <v>126905155</v>
       </c>
       <c r="B25" t="n">
-        <v>57144</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102613</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3216,7 +3216,7 @@
       <c r="K25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>495422</v>
+        <v>495797</v>
       </c>
       <c r="R25" t="n">
-        <v>6906863</v>
+        <v>6906993</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3293,39 +3293,39 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126905144</v>
+        <v>126905228</v>
       </c>
       <c r="B26" t="n">
-        <v>57953</v>
+        <v>57141</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>495384</v>
+        <v>495481</v>
       </c>
       <c r="R26" t="n">
-        <v>6907363</v>
+        <v>6907010</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3402,39 +3402,39 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126905145</v>
+        <v>126905230</v>
       </c>
       <c r="B27" t="n">
-        <v>57953</v>
+        <v>57141</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3444,10 +3444,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>495474</v>
+        <v>495428</v>
       </c>
       <c r="R27" t="n">
-        <v>6907344</v>
+        <v>6907139</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3511,39 +3511,39 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126905147</v>
+        <v>126905234</v>
       </c>
       <c r="B28" t="n">
-        <v>57953</v>
+        <v>57141</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>495488</v>
+        <v>495761</v>
       </c>
       <c r="R28" t="n">
-        <v>6907230</v>
+        <v>6906899</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3620,27 +3620,27 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126905150</v>
+        <v>126905309</v>
       </c>
       <c r="B29" t="n">
-        <v>57953</v>
+        <v>57144</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>102613</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3652,7 +3652,7 @@
       <c r="K29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3662,10 +3662,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495490</v>
+        <v>495781</v>
       </c>
       <c r="R29" t="n">
-        <v>6907214</v>
+        <v>6906930</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3826,32 +3826,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124969222</v>
+        <v>124966657</v>
       </c>
       <c r="B31" t="n">
-        <v>79327</v>
+        <v>79084</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3861,13 +3861,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495735</v>
+        <v>495603</v>
       </c>
       <c r="R31" t="n">
-        <v>6908007</v>
+        <v>6907779</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3894,9 +3894,19 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3911,22 +3921,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Joakim Nilsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Joakim Nilsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124966657</v>
+        <v>124966414</v>
       </c>
       <c r="B32" t="n">
-        <v>79084</v>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3934,21 +3944,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3958,13 +3968,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495603</v>
+        <v>495589</v>
       </c>
       <c r="R32" t="n">
-        <v>6907779</v>
+        <v>6907777</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3991,19 +4001,9 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>12:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4018,19 +4018,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Joakim Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Joakim Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124966414</v>
+        <v>124966467</v>
       </c>
       <c r="B33" t="n">
         <v>80432</v>
@@ -4065,13 +4065,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495589</v>
+        <v>495595</v>
       </c>
       <c r="R33" t="n">
-        <v>6907777</v>
+        <v>6907764</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4098,9 +4098,19 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4115,19 +4125,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Joakim Nilsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Joakim Nilsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124966467</v>
+        <v>124966743</v>
       </c>
       <c r="B34" t="n">
         <v>80432</v>
@@ -4162,10 +4172,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495595</v>
+        <v>495599</v>
       </c>
       <c r="R34" t="n">
-        <v>6907764</v>
+        <v>6907785</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4197,7 +4207,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4207,7 +4217,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4234,7 +4244,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124966743</v>
+        <v>124966816</v>
       </c>
       <c r="B35" t="n">
         <v>80432</v>
@@ -4269,13 +4279,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>495599</v>
+        <v>495611</v>
       </c>
       <c r="R35" t="n">
-        <v>6907785</v>
+        <v>6907812</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4302,19 +4312,9 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>12:26</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4329,19 +4329,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Joakim Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Joakim Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124966816</v>
+        <v>124966882</v>
       </c>
       <c r="B36" t="n">
         <v>80432</v>
@@ -4376,10 +4376,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>495611</v>
+        <v>495615</v>
       </c>
       <c r="R36" t="n">
-        <v>6907812</v>
+        <v>6907826</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4438,7 +4438,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124966882</v>
+        <v>124968063</v>
       </c>
       <c r="B37" t="n">
         <v>80432</v>
@@ -4473,10 +4473,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>495615</v>
+        <v>495609</v>
       </c>
       <c r="R37" t="n">
-        <v>6907826</v>
+        <v>6907780</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4535,7 +4535,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124968063</v>
+        <v>124968117</v>
       </c>
       <c r="B38" t="n">
         <v>80432</v>
@@ -4570,10 +4570,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>495609</v>
+        <v>495600</v>
       </c>
       <c r="R38" t="n">
-        <v>6907780</v>
+        <v>6907771</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4632,48 +4632,57 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124968117</v>
+        <v>124964829</v>
       </c>
       <c r="B39" t="n">
-        <v>80432</v>
+        <v>99142</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>219847</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sjöån, Sjöån, Hjd</t>
+          <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>495600</v>
+        <v>495567</v>
       </c>
       <c r="R39" t="n">
-        <v>6907771</v>
+        <v>6907661</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4687,12 +4696,12 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>Härjedalen</t>
+          <t>Hälsingland</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Överhogdal</t>
+          <t>Ytterhogdal</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -4729,58 +4738,52 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124969190</v>
+        <v>124966132</v>
       </c>
       <c r="B40" t="n">
-        <v>57141</v>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>19</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sjöån, Sjöån, Hls</t>
+          <t>Sjöån, Sjöån, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>495762</v>
+        <v>495562</v>
       </c>
       <c r="R40" t="n">
-        <v>6908016</v>
+        <v>6907725</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4794,12 +4797,12 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>Hälsingland</t>
+          <t>Härjedalen</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>Ytterhogdal</t>
+          <t>Överhogdal</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -4807,9 +4810,19 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4824,69 +4837,60 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Joakim Nilsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Joakim Nilsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124964829</v>
+        <v>124966300</v>
       </c>
       <c r="B41" t="n">
-        <v>99142</v>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sjöån, Sjöån, Hls</t>
+          <t>Sjöån, Sjöån, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>495567</v>
+        <v>495577</v>
       </c>
       <c r="R41" t="n">
-        <v>6907661</v>
+        <v>6907763</v>
       </c>
       <c r="S41" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4900,12 +4904,12 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>Hälsingland</t>
+          <t>Härjedalen</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Ytterhogdal</t>
+          <t>Överhogdal</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -4942,7 +4946,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124966132</v>
+        <v>124966342</v>
       </c>
       <c r="B42" t="n">
         <v>99118</v>
@@ -4970,24 +4974,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>495562</v>
+        <v>495585</v>
       </c>
       <c r="R42" t="n">
-        <v>6907725</v>
+        <v>6907776</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5014,19 +5014,9 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>12:12</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5041,19 +5031,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Joakim Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Joakim Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124966300</v>
+        <v>124966380</v>
       </c>
       <c r="B43" t="n">
         <v>99118</v>
@@ -5081,20 +5071,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>495577</v>
+        <v>495594</v>
       </c>
       <c r="R43" t="n">
-        <v>6907763</v>
+        <v>6907764</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5121,9 +5115,19 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5138,19 +5142,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Joakim Nilsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Joakim Nilsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124966342</v>
+        <v>124966465</v>
       </c>
       <c r="B44" t="n">
         <v>99118</v>
@@ -5185,13 +5189,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>495585</v>
+        <v>495588</v>
       </c>
       <c r="R44" t="n">
-        <v>6907776</v>
+        <v>6907772</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5247,7 +5251,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124966380</v>
+        <v>124966571</v>
       </c>
       <c r="B45" t="n">
         <v>99118</v>
@@ -5277,19 +5281,19 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>35</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sjöån, Sjöån, Hjd</t>
+          <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>495594</v>
+        <v>495604</v>
       </c>
       <c r="R45" t="n">
-        <v>6907764</v>
+        <v>6907750</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5306,12 +5310,12 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>Härjedalen</t>
+          <t>Hälsingland</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Överhogdal</t>
+          <t>Ytterhogdal</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -5321,7 +5325,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5331,7 +5335,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5358,7 +5362,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124966465</v>
+        <v>124966775</v>
       </c>
       <c r="B46" t="n">
         <v>99118</v>
@@ -5393,13 +5397,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>495588</v>
+        <v>495596</v>
       </c>
       <c r="R46" t="n">
-        <v>6907772</v>
+        <v>6907776</v>
       </c>
       <c r="S46" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5426,9 +5430,19 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5443,19 +5457,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Joakim Nilsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Joakim Nilsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124966571</v>
+        <v>124966832</v>
       </c>
       <c r="B47" t="n">
         <v>99118</v>
@@ -5483,21 +5497,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sjöån, Sjöån, Hls</t>
+          <t>Sjöån, Sjöån, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>495604</v>
+        <v>495605</v>
       </c>
       <c r="R47" t="n">
-        <v>6907750</v>
+        <v>6907810</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5514,12 +5524,12 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>Hälsingland</t>
+          <t>Härjedalen</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Ytterhogdal</t>
+          <t>Överhogdal</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -5529,7 +5539,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5539,7 +5549,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5566,7 +5576,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124966775</v>
+        <v>124967045</v>
       </c>
       <c r="B48" t="n">
         <v>99118</v>
@@ -5601,10 +5611,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>495596</v>
+        <v>495626</v>
       </c>
       <c r="R48" t="n">
-        <v>6907776</v>
+        <v>6907819</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5636,7 +5646,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5646,7 +5656,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5673,7 +5683,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124966832</v>
+        <v>124967710</v>
       </c>
       <c r="B49" t="n">
         <v>99118</v>
@@ -5704,17 +5714,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sjöån, Sjöån, Hjd</t>
+          <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>495605</v>
+        <v>495638</v>
       </c>
       <c r="R49" t="n">
-        <v>6907810</v>
+        <v>6907802</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5728,12 +5738,12 @@
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>Härjedalen</t>
+          <t>Hälsingland</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>Överhogdal</t>
+          <t>Ytterhogdal</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
@@ -5741,19 +5751,9 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>12:29</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>12:29</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5768,19 +5768,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Joakim Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Joakim Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124967045</v>
+        <v>124967768</v>
       </c>
       <c r="B50" t="n">
         <v>99118</v>
@@ -5811,17 +5811,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sjöån, Sjöån, Hjd</t>
+          <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>495626</v>
+        <v>495646</v>
       </c>
       <c r="R50" t="n">
-        <v>6907819</v>
+        <v>6907794</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5835,12 +5835,12 @@
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>Härjedalen</t>
+          <t>Hälsingland</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>Överhogdal</t>
+          <t>Ytterhogdal</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
@@ -5848,19 +5848,9 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>12:33</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5875,19 +5865,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Joakim Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Joakim Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124967710</v>
+        <v>124967791</v>
       </c>
       <c r="B51" t="n">
         <v>99118</v>
@@ -5922,10 +5912,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>495638</v>
+        <v>495628</v>
       </c>
       <c r="R51" t="n">
-        <v>6907802</v>
+        <v>6907779</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5984,7 +5974,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124967768</v>
+        <v>124967917</v>
       </c>
       <c r="B52" t="n">
         <v>99118</v>
@@ -6019,13 +6009,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>495646</v>
+        <v>495627</v>
       </c>
       <c r="R52" t="n">
-        <v>6907794</v>
+        <v>6907768</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6081,7 +6071,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124967791</v>
+        <v>124968182</v>
       </c>
       <c r="B53" t="n">
         <v>99118</v>
@@ -6109,17 +6099,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Sjöån, Sjöån, Hls</t>
+          <t>Sjöån, Sjöån, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>495628</v>
+        <v>495595</v>
       </c>
       <c r="R53" t="n">
-        <v>6907779</v>
+        <v>6907770</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6136,12 +6135,12 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>Hälsingland</t>
+          <t>Härjedalen</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>Ytterhogdal</t>
+          <t>Överhogdal</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
@@ -6178,7 +6177,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124967917</v>
+        <v>124968251</v>
       </c>
       <c r="B54" t="n">
         <v>99118</v>
@@ -6206,17 +6205,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sjöån, Sjöån, Hls</t>
+          <t>Sjöån, Sjöån, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>495627</v>
+        <v>495597</v>
       </c>
       <c r="R54" t="n">
-        <v>6907768</v>
+        <v>6907770</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6233,12 +6241,12 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>Hälsingland</t>
+          <t>Härjedalen</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>Ytterhogdal</t>
+          <t>Överhogdal</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
@@ -6275,7 +6283,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124968182</v>
+        <v>124968326</v>
       </c>
       <c r="B55" t="n">
         <v>99118</v>
@@ -6319,13 +6327,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>495595</v>
+        <v>495600</v>
       </c>
       <c r="R55" t="n">
-        <v>6907770</v>
+        <v>6907758</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6381,57 +6389,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124968251</v>
+        <v>124968696</v>
       </c>
       <c r="B56" t="n">
-        <v>99118</v>
+        <v>79085</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sjöån, Sjöån, Hjd</t>
+          <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>495597</v>
+        <v>495755</v>
       </c>
       <c r="R56" t="n">
-        <v>6907770</v>
+        <v>6907825</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6445,12 +6444,12 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>Härjedalen</t>
+          <t>Hälsingland</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>Överhogdal</t>
+          <t>Ytterhogdal</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
@@ -6487,54 +6486,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124968326</v>
+        <v>124966724</v>
       </c>
       <c r="B57" t="n">
-        <v>99118</v>
+        <v>80392</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Sjöån, Sjöån, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>495600</v>
+        <v>495599</v>
       </c>
       <c r="R57" t="n">
-        <v>6907758</v>
+        <v>6907785</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6564,9 +6554,19 @@
           <t>2025-05-11</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6581,57 +6581,57 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Joakim Nilsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Joakim Nilsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124968696</v>
+        <v>124969222</v>
       </c>
       <c r="B58" t="n">
-        <v>79085</v>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sjöån, Sjöån, Hls</t>
+          <t>Sjöån, Sjöån, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>495755</v>
+        <v>495735</v>
       </c>
       <c r="R58" t="n">
-        <v>6907825</v>
+        <v>6908007</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>Hälsingland</t>
+          <t>Härjedalen</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>Ytterhogdal</t>
+          <t>Överhogdal</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
@@ -6690,45 +6690,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124966724</v>
+        <v>124941900</v>
       </c>
       <c r="B59" t="n">
-        <v>80392</v>
+        <v>79946</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229497</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sjöån, Sjöån, Hjd</t>
+          <t>Storkullen, Storkullen, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>495599</v>
+        <v>495837</v>
       </c>
       <c r="R59" t="n">
-        <v>6907785</v>
+        <v>6908175</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6755,22 +6755,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6785,22 +6775,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Joakim Nilsson</t>
+          <t>Joel Schill</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Joakim Nilsson</t>
+          <t>Joel Schill</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124941900</v>
+        <v>124974531</v>
       </c>
       <c r="B60" t="n">
-        <v>79946</v>
+        <v>78334</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6808,21 +6798,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6832,10 +6822,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>495837</v>
+        <v>495932</v>
       </c>
       <c r="R60" t="n">
-        <v>6908175</v>
+        <v>6908352</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6862,12 +6852,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6882,60 +6882,70 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Joel Schill</t>
+          <t>Joakim Nilsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Joel Schill</t>
+          <t>Joakim Nilsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124974531</v>
+        <v>124969190</v>
       </c>
       <c r="B61" t="n">
-        <v>78334</v>
+        <v>57141</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6487</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Storkullen, Storkullen, Hjd</t>
+          <t>Sjöån, Sjöån, Hls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>495932</v>
+        <v>495762</v>
       </c>
       <c r="R61" t="n">
-        <v>6908352</v>
+        <v>6908016</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6949,12 +6959,12 @@
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>Härjedalen</t>
+          <t>Hälsingland</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>Överhogdal</t>
+          <t>Ytterhogdal</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
@@ -6962,19 +6972,9 @@
           <t>2025-05-11</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>15:29</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6989,39 +6989,39 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Joakim Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Joakim Nilsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126905160</v>
+        <v>126905285</v>
       </c>
       <c r="B62" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7029,11 +7029,15 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -7043,10 +7047,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>496024</v>
+        <v>496205</v>
       </c>
       <c r="R62" t="n">
-        <v>6906682</v>
+        <v>6906779</v>
       </c>
       <c r="S62" t="n">
         <v>50</v>
@@ -7110,39 +7114,39 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126905241</v>
+        <v>126905160</v>
       </c>
       <c r="B63" t="n">
-        <v>57141</v>
+        <v>57953</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -7152,10 +7156,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>496498</v>
+        <v>496024</v>
       </c>
       <c r="R63" t="n">
-        <v>6906538</v>
+        <v>6906682</v>
       </c>
       <c r="S63" t="n">
         <v>50</v>
@@ -7219,7 +7223,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126905242</v>
+        <v>126905240</v>
       </c>
       <c r="B64" t="n">
         <v>57141</v>
@@ -7261,10 +7265,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>496465</v>
+        <v>496205</v>
       </c>
       <c r="R64" t="n">
-        <v>6906496</v>
+        <v>6906779</v>
       </c>
       <c r="S64" t="n">
         <v>50</v>
@@ -7328,7 +7332,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126905243</v>
+        <v>126905241</v>
       </c>
       <c r="B65" t="n">
         <v>57141</v>
@@ -7370,10 +7374,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>496446</v>
+        <v>496498</v>
       </c>
       <c r="R65" t="n">
-        <v>6906461</v>
+        <v>6906538</v>
       </c>
       <c r="S65" t="n">
         <v>50</v>
@@ -7437,10 +7441,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126905315</v>
+        <v>126905242</v>
       </c>
       <c r="B66" t="n">
-        <v>57144</v>
+        <v>57141</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7448,21 +7452,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>102613</v>
+        <v>100138</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7479,10 +7483,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>496443</v>
+        <v>496465</v>
       </c>
       <c r="R66" t="n">
-        <v>6906614</v>
+        <v>6906496</v>
       </c>
       <c r="S66" t="n">
         <v>50</v>
@@ -7546,10 +7550,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126905285</v>
+        <v>126905243</v>
       </c>
       <c r="B67" t="n">
-        <v>57950</v>
+        <v>57141</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7557,32 +7561,28 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -7592,10 +7592,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>496205</v>
+        <v>496446</v>
       </c>
       <c r="R67" t="n">
-        <v>6906779</v>
+        <v>6906461</v>
       </c>
       <c r="S67" t="n">
         <v>50</v>
@@ -7659,10 +7659,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126905240</v>
+        <v>126905315</v>
       </c>
       <c r="B68" t="n">
-        <v>57141</v>
+        <v>57144</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7670,21 +7670,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100138</v>
+        <v>102613</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7701,10 +7701,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>496205</v>
+        <v>496443</v>
       </c>
       <c r="R68" t="n">
-        <v>6906779</v>
+        <v>6906614</v>
       </c>
       <c r="S68" t="n">
         <v>50</v>
@@ -8452,10 +8452,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>97023527</v>
+        <v>97023516</v>
       </c>
       <c r="B75" t="n">
-        <v>91909</v>
+        <v>91831</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8463,21 +8463,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>3242</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8487,10 +8487,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>496458</v>
+        <v>496480</v>
       </c>
       <c r="R75" t="n">
-        <v>6907525</v>
+        <v>6907307</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8536,7 +8536,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>gammal och tät barrnaturskog uppkommen efter brand</t>
+          <t>ljus, olikåldrig tallnaturskog på blockig, fuktig mark</t>
         </is>
       </c>
       <c r="AN75" t="n">
@@ -8544,7 +8544,7 @@
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad granlåga</t>
+          <t>1 substratenheter # torraka som hänger på björk</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -8566,32 +8566,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>97023516</v>
+        <v>97023515</v>
       </c>
       <c r="B76" t="n">
-        <v>91831</v>
+        <v>92152</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>3242</v>
+        <v>5260</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8601,10 +8601,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>496480</v>
+        <v>496479</v>
       </c>
       <c r="R76" t="n">
-        <v>6907307</v>
+        <v>6907316</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8658,7 +8658,7 @@
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>1 substratenheter # torraka som hänger på björk</t>
+          <t>1 substratenheter # fallen torraka som hänger på block</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -8680,7 +8680,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>97023515</v>
+        <v>97023519</v>
       </c>
       <c r="B77" t="n">
         <v>92152</v>
@@ -8715,10 +8715,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>496479</v>
+        <v>496463</v>
       </c>
       <c r="R77" t="n">
-        <v>6907316</v>
+        <v>6907294</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8764,7 +8764,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>ljus, olikåldrig tallnaturskog på blockig, fuktig mark</t>
+          <t>olikåldrig tallnaturskog på fuktig mark</t>
         </is>
       </c>
       <c r="AN77" t="n">
@@ -8772,7 +8772,7 @@
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>1 substratenheter # fallen torraka som hänger på block</t>
+          <t>1 substratenheter # gammal tallåga upphängd på en ännu äldre, även gullgröppa och timmerticka alldeles bredvid på lågan, citronticka och fläckporing på andra delar, samt ett vitt skinn</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -8794,32 +8794,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>97023519</v>
+        <v>97023518</v>
       </c>
       <c r="B78" t="n">
-        <v>92152</v>
+        <v>91282</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5260</v>
+        <v>5685</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal tallåga upphängd på en ännu äldre, även gullgröppa och timmerticka alldeles bredvid på lågan, citronticka och fläckporing på andra delar, samt ett vitt skinn</t>
+          <t>1 substratenheter # gammal tallåga upphängd på ännu äldre</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -8908,32 +8908,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>97023518</v>
+        <v>97023521</v>
       </c>
       <c r="B79" t="n">
-        <v>91282</v>
+        <v>79084</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5685</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8943,10 +8943,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>496463</v>
+        <v>496507</v>
       </c>
       <c r="R79" t="n">
-        <v>6907294</v>
+        <v>6907260</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8992,7 +8992,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>olikåldrig tallnaturskog på fuktig mark</t>
+          <t>halvgammal barrnaturskog på fuktig mark</t>
         </is>
       </c>
       <c r="AN79" t="n">
@@ -9000,7 +9000,7 @@
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal tallåga upphängd på ännu äldre</t>
+          <t>1 substratenheter # grov brandhögstubbe</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9022,10 +9022,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>97023521</v>
+        <v>97023522</v>
       </c>
       <c r="B80" t="n">
-        <v>79084</v>
+        <v>79917</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9033,21 +9033,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9057,10 +9057,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>496507</v>
+        <v>496520</v>
       </c>
       <c r="R80" t="n">
-        <v>6907260</v>
+        <v>6907290</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9106,7 +9106,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>halvgammal barrnaturskog på fuktig mark</t>
+          <t>ljus, halvgammal tallnaturskog</t>
         </is>
       </c>
       <c r="AN80" t="n">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov brandhögstubbe</t>
+          <t>1 substratenheter # torraka, 30 cm bred</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9136,7 +9136,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>97023522</v>
+        <v>97023526</v>
       </c>
       <c r="B81" t="n">
         <v>79917</v>
@@ -9171,10 +9171,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>496520</v>
+        <v>496492</v>
       </c>
       <c r="R81" t="n">
-        <v>6907290</v>
+        <v>6907330</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>ljus, halvgammal tallnaturskog</t>
+          <t>ljus, halvgammal barrnaturskog</t>
         </is>
       </c>
       <c r="AN81" t="n">
@@ -9250,10 +9250,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>97023526</v>
+        <v>97023527</v>
       </c>
       <c r="B82" t="n">
-        <v>79917</v>
+        <v>91909</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9261,21 +9261,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9285,10 +9285,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>496492</v>
+        <v>496458</v>
       </c>
       <c r="R82" t="n">
-        <v>6907330</v>
+        <v>6907525</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>ljus, halvgammal barrnaturskog</t>
+          <t>gammal och tät barrnaturskog uppkommen efter brand</t>
         </is>
       </c>
       <c r="AN82" t="n">
@@ -9342,7 +9342,7 @@
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>1 substratenheter # torraka, 30 cm bred</t>
+          <t>1 substratenheter # förrötad granlåga</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
